--- a/artfynd/A 63000-2025 artfynd.xlsx
+++ b/artfynd/A 63000-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305117</v>
       </c>
       <c r="B2" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305115</v>
       </c>
       <c r="B3" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63000-2025 artfynd.xlsx
+++ b/artfynd/A 63000-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305117</v>
       </c>
       <c r="B2" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305115</v>
       </c>
       <c r="B3" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63000-2025 artfynd.xlsx
+++ b/artfynd/A 63000-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305117</v>
       </c>
       <c r="B2" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305115</v>
       </c>
       <c r="B3" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63000-2025 artfynd.xlsx
+++ b/artfynd/A 63000-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305117</v>
       </c>
       <c r="B2" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305115</v>
       </c>
       <c r="B3" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63000-2025 artfynd.xlsx
+++ b/artfynd/A 63000-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305117</v>
       </c>
       <c r="B2" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305115</v>
       </c>
       <c r="B3" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63000-2025 artfynd.xlsx
+++ b/artfynd/A 63000-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305117</v>
       </c>
       <c r="B2" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305115</v>
       </c>
       <c r="B3" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63000-2025 artfynd.xlsx
+++ b/artfynd/A 63000-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137305117</v>
+        <v>137512058</v>
       </c>
       <c r="B2" t="n">
-        <v>87556</v>
+        <v>75519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3674</v>
+        <v>1116</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kappelshamn, Gtl</t>
+          <t>Flenvike, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>722747</v>
+        <v>722693</v>
       </c>
       <c r="R2" t="n">
-        <v>6419466</v>
+        <v>6419509</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,49 +765,49 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137305117</t>
+          <t>https://artportalen.se/Sighting/137512058</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137305115</v>
+        <v>137305117</v>
       </c>
       <c r="B3" t="n">
-        <v>87417</v>
+        <v>87556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>722731</v>
+        <v>722747</v>
       </c>
       <c r="R3" t="n">
-        <v>6419501</v>
+        <v>6419466</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,7 +871,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,7 +888,222 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137305117</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137305115</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87417</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kappelshamn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>722731</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6419501</v>
+      </c>
+      <c r="S4" t="n">
+        <v>14</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137305115</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137512126</v>
+      </c>
+      <c r="B5" t="n">
+        <v>87594</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flenvike, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>722708</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6419504</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137512126</t>
         </is>
       </c>
     </row>
@@ -907,6 +1111,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63000-2025 artfynd.xlsx
+++ b/artfynd/A 63000-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137512058</v>
       </c>
       <c r="B2" t="n">
-        <v>75519</v>
+        <v>75522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137305117</v>
       </c>
       <c r="B3" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137305115</v>
       </c>
       <c r="B4" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>137512126</v>
       </c>
       <c r="B5" t="n">
-        <v>87594</v>
+        <v>87597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
